--- a/public/samples/es/sample2.xlsx
+++ b/public/samples/es/sample2.xlsx
@@ -35,7 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,10 +79,11 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +502,7 @@
       <c r="C3" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>6.3</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -519,7 +522,7 @@
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>4.2</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -539,7 +542,7 @@
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>5.6</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -559,7 +562,7 @@
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>5.4</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -579,7 +582,7 @@
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>5.6</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -599,7 +602,7 @@
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>5.8</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -619,7 +622,7 @@
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>6.5</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -639,7 +642,7 @@
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>5.6</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -659,7 +662,7 @@
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>5.2</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -679,7 +682,7 @@
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>4.9</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -699,7 +702,7 @@
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>5.2</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -719,7 +722,7 @@
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>5.5</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -739,7 +742,7 @@
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>5.3</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -759,7 +762,7 @@
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>5.8</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -779,7 +782,7 @@
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>4.9</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -799,7 +802,7 @@
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>4.9</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -819,7 +822,7 @@
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>5.5</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -839,7 +842,7 @@
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>6.1</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -859,7 +862,7 @@
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>5.1</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -879,7 +882,7 @@
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>5.7</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -899,7 +902,7 @@
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>5.2</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -919,7 +922,7 @@
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>5.3</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -939,7 +942,7 @@
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>5.4</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -959,7 +962,7 @@
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>4.8</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -979,7 +982,7 @@
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>5.2</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -999,7 +1002,7 @@
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>5.8</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1019,7 +1022,7 @@
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>6.7</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1039,7 +1042,7 @@
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>5.5</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -1059,7 +1062,7 @@
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>5.2</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -1079,7 +1082,7 @@
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>4.2</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -1099,7 +1102,7 @@
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <v>4.7</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -1119,7 +1122,7 @@
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>6.6</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -1139,7 +1142,7 @@
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
         <v>6.1</v>
       </c>
       <c r="E35" s="2" t="str">
@@ -1159,7 +1162,7 @@
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>5.4</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -1179,7 +1182,7 @@
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>6.1</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -1199,7 +1202,7 @@
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>5.6</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -1219,7 +1222,7 @@
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>5.2</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -1239,7 +1242,7 @@
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <v>5.4</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -1259,7 +1262,7 @@
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>5.7</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -1279,7 +1282,7 @@
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>5.9</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -1299,7 +1302,7 @@
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>5.7</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -1319,7 +1322,7 @@
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>5.8</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -1339,7 +1342,7 @@
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>6.3</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -1359,7 +1362,7 @@
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>5.6</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -1379,7 +1382,7 @@
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>4.7</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -1399,7 +1402,7 @@
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>5.9</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -1419,7 +1422,7 @@
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>4.9</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -1439,8 +1442,8 @@
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D50" s="2" t="str">
-        <v>6.0</v>
+      <c r="D50" s="3">
+        <v>6</v>
       </c>
       <c r="E50" s="2" t="str">
         <v/>
@@ -1459,7 +1462,7 @@
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>5.3</v>
       </c>
       <c r="E51" s="2" t="str">
@@ -1479,8 +1482,8 @@
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D52" s="2" t="str">
-        <v>5.0</v>
+      <c r="D52" s="3">
+        <v>5</v>
       </c>
       <c r="E52" s="2" t="str">
         <v/>
@@ -1499,7 +1502,7 @@
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="3">
         <v>5.6</v>
       </c>
       <c r="E53" s="2" t="str">
@@ -1519,7 +1522,7 @@
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>5.6</v>
       </c>
       <c r="E54" s="2" t="str">
@@ -1539,7 +1542,7 @@
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <v>5.6</v>
       </c>
       <c r="E55" s="2" t="str">
@@ -1559,7 +1562,7 @@
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <v>4.9</v>
       </c>
       <c r="E56" s="2" t="str">
@@ -1579,7 +1582,7 @@
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>6.2</v>
       </c>
       <c r="E57" s="2" t="str">
@@ -1599,7 +1602,7 @@
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <v>4.5</v>
       </c>
       <c r="E58" s="2" t="str">
@@ -1619,7 +1622,7 @@
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>5.1</v>
       </c>
       <c r="E59" s="2" t="str">
@@ -1639,7 +1642,7 @@
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>6.2</v>
       </c>
       <c r="E60" s="2" t="str">
@@ -1659,7 +1662,7 @@
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
         <v>5.8</v>
       </c>
       <c r="E61" s="2" t="str">
@@ -1679,7 +1682,7 @@
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
         <v>5.4</v>
       </c>
       <c r="E62" s="2" t="str">
@@ -1699,8 +1702,8 @@
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D63" s="2" t="str">
-        <v>6.0</v>
+      <c r="D63" s="3">
+        <v>6</v>
       </c>
       <c r="E63" s="2" t="str">
         <v/>
@@ -1719,7 +1722,7 @@
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>5.3</v>
       </c>
       <c r="E64" s="2" t="str">
@@ -1739,7 +1742,7 @@
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
         <v>5.1</v>
       </c>
       <c r="E65" s="2" t="str">
@@ -1759,7 +1762,7 @@
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
         <v>5.3</v>
       </c>
       <c r="E66" s="2" t="str">
@@ -1779,7 +1782,7 @@
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
         <v>5.2</v>
       </c>
       <c r="E67" s="2" t="str">
@@ -1799,7 +1802,7 @@
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="3">
         <v>5.2</v>
       </c>
       <c r="E68" s="2" t="str">
@@ -1819,7 +1822,7 @@
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
         <v>5.6</v>
       </c>
       <c r="E69" s="2" t="str">
@@ -1839,7 +1842,7 @@
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="3">
         <v>4.7</v>
       </c>
       <c r="E70" s="2" t="str">
@@ -1859,7 +1862,7 @@
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3">
         <v>5.6</v>
       </c>
       <c r="E71" s="2" t="str">
@@ -1879,7 +1882,7 @@
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="3">
         <v>5.7</v>
       </c>
       <c r="E72" s="2" t="str">
@@ -1899,7 +1902,7 @@
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="3">
         <v>5.8</v>
       </c>
       <c r="E73" s="2" t="str">
@@ -1919,7 +1922,7 @@
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="3">
         <v>5.4</v>
       </c>
       <c r="E74" s="2" t="str">
@@ -1939,7 +1942,7 @@
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="3">
         <v>5.1</v>
       </c>
       <c r="E75" s="2" t="str">
@@ -1959,7 +1962,7 @@
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="3">
         <v>6.4</v>
       </c>
       <c r="E76" s="2" t="str">
@@ -1979,7 +1982,7 @@
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="3">
         <v>5.8</v>
       </c>
       <c r="E77" s="2" t="str">
@@ -1999,7 +2002,7 @@
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="3">
         <v>5.1</v>
       </c>
       <c r="E78" s="2" t="str">
@@ -2019,7 +2022,7 @@
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="3">
         <v>6.1</v>
       </c>
       <c r="E79" s="2" t="str">
@@ -2039,7 +2042,7 @@
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="3">
         <v>5.1</v>
       </c>
       <c r="E80" s="2" t="str">
@@ -2059,7 +2062,7 @@
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="3">
         <v>5.6</v>
       </c>
       <c r="E81" s="2" t="str">
@@ -2079,7 +2082,7 @@
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="3">
         <v>5.1</v>
       </c>
       <c r="E82" s="2" t="str">

--- a/public/samples/es/sample2.xlsx
+++ b/public/samples/es/sample2.xlsx
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +471,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +489,12 @@
         <v>Promedio de notas</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>NEE (PIE)</v>
+        <v>Nivel de matemática</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Grupo de origen</v>
       </c>
     </row>
@@ -497,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Sofía Castro</v>
+        <v>Sofía González</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +511,14 @@
       <c r="D3" s="3">
         <v>6.3</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="4">
@@ -517,18 +526,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Mateo Martínez</v>
+        <v>Mateo Vargas</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>4.6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -537,19 +549,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Valentina Jiménez</v>
+        <v>Valentina Muñoz</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="6">
@@ -563,13 +578,16 @@
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +595,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Isabella González</v>
+        <v>Isabella Castro</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="8">
@@ -597,19 +618,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Sebastián Jiménez</v>
+        <v>Sebastián Silva</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D8" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="9">
@@ -617,19 +641,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Camila Silva</v>
+        <v>Camila Flores</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="10">
@@ -637,19 +664,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Matías González</v>
+        <v>Matías Rodríguez</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E10" s="2" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F10" s="2" t="str">
-        <v>D</v>
+      <c r="G10" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +687,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Mariana González</v>
+        <v>Mariana Flores</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="12">
@@ -677,19 +710,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Benjamín Díaz</v>
+        <v>Benjamín Castro</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +733,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Lucía Rojas</v>
+        <v>Lucía Sánchez</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="14">
@@ -717,19 +756,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Nicolás Pérez</v>
+        <v>Nicolás Castro</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="15">
@@ -737,19 +779,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Martina Pérez</v>
+        <v>Martina Sánchez</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="16">
@@ -757,18 +802,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Tomás Castro</v>
+        <v>Tomás Muñoz</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>4.8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -777,19 +825,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Daniela Rodríguez</v>
+        <v>Daniela Castro</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>5.4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +848,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Joaquín Ramírez</v>
+        <v>Joaquín Silva</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -817,18 +871,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Gabriela Rodríguez</v>
+        <v>Gabriela López</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -837,18 +894,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Diego Morales</v>
+        <v>Diego López</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -863,13 +923,16 @@
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="22">
@@ -877,19 +940,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Emiliano Sánchez</v>
+        <v>Emiliano Pérez</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="23">
@@ -897,18 +963,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Renata López</v>
+        <v>Renata Martínez</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>4.6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -917,18 +986,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Gabriel Castro</v>
+        <v>Gabriel Rojas</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v>✓</v>
+        <v>5.7</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -937,19 +1009,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Emilia Muñoz</v>
+        <v>Emilia Vargas</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E25" s="2">
+        <v>5</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="26">
@@ -957,18 +1032,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Torres</v>
+        <v>Lucas Herrera</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -977,7 +1055,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Florencia Herrera</v>
+        <v>Florencia Pérez</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
@@ -985,11 +1063,14 @@
       <c r="D27" s="3">
         <v>5.2</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="28">
@@ -997,19 +1078,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Martín Rojas</v>
+        <v>Martín González</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1101,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Paula Castro</v>
+        <v>Paula Vargas</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="30">
@@ -1037,7 +1124,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Felipe Herrera</v>
+        <v>Felipe Jiménez</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
@@ -1045,11 +1132,14 @@
       <c r="D30" s="3">
         <v>5.5</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1057,18 +1147,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Antonella Muñoz</v>
+        <v>Antonella Flores</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
       </c>
       <c r="F31" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1077,18 +1170,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Alejandro Díaz</v>
+        <v>Alejandro Morales</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1097,18 +1193,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Josefa Martínez</v>
+        <v>Josefa Pérez</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E33" s="2" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F33" s="2" t="str">
+      <c r="G33" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1117,19 +1216,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Samuel Ramírez</v>
+        <v>Samuel Sánchez</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="35">
@@ -1137,19 +1239,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Catalina Díaz</v>
+        <v>Catalina Pérez</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="36">
@@ -1157,19 +1262,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Agustín Rodríguez</v>
+        <v>Agustín López</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="37">
@@ -1177,19 +1285,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ximena Morales</v>
+        <v>Ximena Castro</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="38">
@@ -1197,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Daniel Muñoz</v>
+        <v>Daniel Martínez</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
@@ -1205,10 +1316,13 @@
       <c r="D38" s="3">
         <v>5.6</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1217,18 +1331,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Julieta Muñoz</v>
+        <v>Julieta González</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4</v>
       </c>
       <c r="F39" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1237,18 +1354,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Maximiliano Martínez</v>
+        <v>Maximiliano Pérez</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
       </c>
       <c r="F40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1257,19 +1377,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Agustina Morales</v>
+        <v>Agustina Herrera</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="42">
@@ -1277,19 +1400,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Vicente Vargas</v>
+        <v>Vicente Pérez</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="43">
@@ -1297,19 +1423,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Sofía López</v>
+        <v>Sofía Pérez</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E43" s="2">
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="44">
@@ -1317,19 +1446,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Santiago Romero</v>
+        <v>Mateo González</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="45">
@@ -1337,19 +1469,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Valentina González</v>
+        <v>Valentina Pérez</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E45" s="2">
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="46">
@@ -1357,18 +1492,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Sebastián Herrera</v>
+        <v>Santiago Díaz</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1377,19 +1515,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Isabella Martínez</v>
+        <v>Camila Silva</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1397,19 +1538,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Matías Díaz</v>
+        <v>Sebastián Pérez</v>
       </c>
       <c r="C48" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D48" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>5</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="49">
@@ -1417,18 +1561,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Camila Vargas</v>
+        <v>Mariana Díaz</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>4.8</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1437,19 +1584,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Benjamín Flores</v>
+        <v>Matías Castro</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="3">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="51">
@@ -1457,18 +1607,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Mariana Rojas</v>
+        <v>Lucía Flores</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>4.4</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1477,19 +1630,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Tomás Jiménez</v>
+        <v>Benjamín Martínez</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="3">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="53">
@@ -1497,19 +1653,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Lucía Díaz</v>
+        <v>Martina Silva</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="54">
@@ -1517,19 +1676,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Diego Castro</v>
+        <v>Nicolás Jiménez</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="55">
@@ -1537,19 +1699,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Martina Gutiérrez</v>
+        <v>Daniela Herrera</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>4</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="56">
@@ -1557,18 +1722,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Emiliano González</v>
+        <v>Joaquín Flores</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>4.7</v>
+      </c>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1577,19 +1745,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Daniela Díaz</v>
+        <v>Gabriela Castro</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="58">
@@ -1597,19 +1768,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Gabriel Ramírez</v>
+        <v>Diego Rodríguez</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="59">
@@ -1617,19 +1791,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Gabriela Silva</v>
+        <v>Victoria Romero</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="60">
@@ -1637,19 +1814,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Lucas Martínez</v>
+        <v>Emiliano Rojas</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="61">
@@ -1657,19 +1837,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Victoria Jiménez</v>
+        <v>Renata Romero</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="62">
@@ -1677,19 +1860,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Martín Jiménez</v>
+        <v>Gabriel Díaz</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="63">
@@ -1697,18 +1883,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Renata Muñoz</v>
+        <v>Emilia González</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="3">
-        <v>6</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E63" s="2">
+        <v>3</v>
       </c>
       <c r="F63" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1717,19 +1906,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Felipe Rodríguez</v>
+        <v>Lucas Jiménez</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G64" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="65">
@@ -1737,7 +1929,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Florencia Ramírez</v>
+        <v>Florencia Herrera</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
@@ -1745,10 +1937,13 @@
       <c r="D65" s="3">
         <v>5.1</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1757,18 +1952,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Alejandro López</v>
+        <v>Martín Morales</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E66" s="2">
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1777,18 +1975,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Paula Rodríguez</v>
+        <v>Paula Pérez</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1797,18 +1998,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Samuel Silva</v>
+        <v>Felipe Silva</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1817,19 +2021,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Antonella Herrera</v>
+        <v>Antonella Díaz</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="70">
@@ -1837,19 +2044,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Agustín Castro</v>
+        <v>Alejandro Silva</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="71">
@@ -1857,19 +2067,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Josefa Vargas</v>
+        <v>Josefa Morales</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E71" s="2">
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="72">
@@ -1877,19 +2090,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Daniel Herrera</v>
+        <v>Agustín Vargas</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -1897,19 +2113,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Catalina Rodríguez</v>
+        <v>Catalina Jiménez</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v>✓</v>
+        <v>5.4</v>
+      </c>
+      <c r="E73" s="2">
+        <v>4</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1917,19 +2136,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Maximiliano Jiménez</v>
+        <v>Daniel Silva</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v>✓</v>
+        <v>5.7</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="75">
@@ -1937,19 +2159,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Ximena Flores</v>
+        <v>Ximena Martínez</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="76">
@@ -1957,19 +2182,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Vicente Gutiérrez</v>
+        <v>Maximiliano Morales</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E76" s="2">
+        <v>5</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="77">
@@ -1977,18 +2205,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Julieta Morales</v>
+        <v>Julieta Rojas</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
       </c>
       <c r="F77" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1997,19 +2228,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Mateo Vargas</v>
+        <v>Vicente Silva</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="79">
@@ -2017,19 +2251,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Agustina Romero</v>
+        <v>Agustina Ramírez</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="80">
@@ -2037,19 +2274,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Sebastián Romero</v>
+        <v>Mateo Morales</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E80" s="2">
+        <v>4</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="81">
@@ -2057,18 +2297,21 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Sofía Herrera</v>
+        <v>Sofía Rojas</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E81" s="2">
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -2077,24 +2320,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Matías Morales</v>
+        <v>Santiago Pérez</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>4.3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2105,13 +2351,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2127,21 +2373,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/es/sample2.xlsx
+++ b/public/samples/es/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de estudiantes" sheetId="2" r:id="rId2"/>
     <sheet name="Mantener juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Criterios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -621,7 +622,7 @@
         <v>Sebastián Silva</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D8" s="3">
         <v>6.5</v>
@@ -966,7 +967,7 @@
         <v>Renata Martínez</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D23" s="3">
         <v>4.6</v>
@@ -1541,7 +1542,7 @@
         <v>Sebastián Pérez</v>
       </c>
       <c r="C48" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D48" s="3">
         <v>5.1</v>
@@ -1886,7 +1887,7 @@
         <v>Emilia González</v>
       </c>
       <c r="C63" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D63" s="3">
         <v>5.9</v>
@@ -2395,4 +2396,87 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Criterio</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opciones</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Género</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Promedio de notas</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nivel de matemática</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nivel</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Grupo de origen</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/es/sample2.xlsx
+++ b/public/samples/es/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de estudiantes" sheetId="2" r:id="rId2"/>
     <sheet name="Mantener juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Criterios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -450,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -471,6 +472,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -486,9 +490,12 @@
         <v>Promedio de notas</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>NEE (PIE)</v>
+        <v>Nivel de matemática</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>Grupo de origen</v>
       </c>
     </row>
@@ -497,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>Sofía Castro</v>
+        <v>Sofía González</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>F</v>
@@ -505,11 +512,14 @@
       <c r="D3" s="3">
         <v>6.3</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="4">
@@ -517,18 +527,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Mateo Martínez</v>
+        <v>Mateo Vargas</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D4" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>4.6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -537,19 +550,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Valentina Jiménez</v>
+        <v>Valentina Muñoz</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D5" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="6">
@@ -563,13 +579,16 @@
         <v>M</v>
       </c>
       <c r="D6" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +596,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Isabella González</v>
+        <v>Isabella Castro</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D7" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="8">
@@ -597,19 +619,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Sebastián Jiménez</v>
+        <v>Sebastián Silva</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D8" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="9">
@@ -617,19 +642,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Camila Silva</v>
+        <v>Camila Flores</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D9" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="10">
@@ -637,19 +665,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Matías González</v>
+        <v>Matías Rodríguez</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D10" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E10" s="2" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F10" s="2" t="str">
-        <v>D</v>
+      <c r="G10" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +688,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Mariana González</v>
+        <v>Mariana Flores</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D11" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="12">
@@ -677,19 +711,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Benjamín Díaz</v>
+        <v>Benjamín Castro</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D12" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +734,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Lucía Rojas</v>
+        <v>Lucía Sánchez</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D13" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="14">
@@ -717,19 +757,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Nicolás Pérez</v>
+        <v>Nicolás Castro</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D14" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="15">
@@ -737,19 +780,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Martina Pérez</v>
+        <v>Martina Sánchez</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D15" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="16">
@@ -757,18 +803,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Tomás Castro</v>
+        <v>Tomás Muñoz</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D16" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>4.8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -777,19 +826,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Daniela Rodríguez</v>
+        <v>Daniela Castro</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D17" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>5.4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="18">
@@ -797,18 +849,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Joaquín Ramírez</v>
+        <v>Joaquín Silva</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D18" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -817,18 +872,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Gabriela Rodríguez</v>
+        <v>Gabriela López</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D19" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -837,18 +895,21 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Diego Morales</v>
+        <v>Diego López</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D20" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -863,13 +924,16 @@
         <v>F</v>
       </c>
       <c r="D21" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="22">
@@ -877,19 +941,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Emiliano Sánchez</v>
+        <v>Emiliano Pérez</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D22" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="23">
@@ -897,18 +964,21 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Renata López</v>
+        <v>Renata Martínez</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D23" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>4.6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -917,18 +987,21 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Gabriel Castro</v>
+        <v>Gabriel Rojas</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v>✓</v>
+        <v>5.7</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -937,19 +1010,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Emilia Muñoz</v>
+        <v>Emilia Vargas</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E25" s="2">
+        <v>5</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="26">
@@ -957,18 +1033,21 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Lucas Torres</v>
+        <v>Lucas Herrera</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -977,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Florencia Herrera</v>
+        <v>Florencia Pérez</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
@@ -985,11 +1064,14 @@
       <c r="D27" s="3">
         <v>5.2</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="28">
@@ -997,19 +1079,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Martín Rojas</v>
+        <v>Martín González</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="29">
@@ -1017,19 +1102,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Paula Castro</v>
+        <v>Paula Vargas</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="30">
@@ -1037,7 +1125,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Felipe Herrera</v>
+        <v>Felipe Jiménez</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
@@ -1045,11 +1133,14 @@
       <c r="D30" s="3">
         <v>5.5</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="31">
@@ -1057,18 +1148,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Antonella Muñoz</v>
+        <v>Antonella Flores</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
       </c>
       <c r="F31" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1077,18 +1171,21 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Alejandro Díaz</v>
+        <v>Alejandro Morales</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1097,18 +1194,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Josefa Martínez</v>
+        <v>Josefa Pérez</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E33" s="2" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F33" s="2" t="str">
+      <c r="G33" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1117,19 +1217,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Samuel Ramírez</v>
+        <v>Samuel Sánchez</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="35">
@@ -1137,19 +1240,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Catalina Díaz</v>
+        <v>Catalina Pérez</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="36">
@@ -1157,19 +1263,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Agustín Rodríguez</v>
+        <v>Agustín López</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="37">
@@ -1177,19 +1286,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ximena Morales</v>
+        <v>Ximena Castro</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="38">
@@ -1197,7 +1309,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Daniel Muñoz</v>
+        <v>Daniel Martínez</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
@@ -1205,10 +1317,13 @@
       <c r="D38" s="3">
         <v>5.6</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1217,18 +1332,21 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Julieta Muñoz</v>
+        <v>Julieta González</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4</v>
       </c>
       <c r="F39" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1237,18 +1355,21 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Maximiliano Martínez</v>
+        <v>Maximiliano Pérez</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
       </c>
       <c r="F40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1257,19 +1378,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Agustina Morales</v>
+        <v>Agustina Herrera</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D41" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="42">
@@ -1277,19 +1401,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Vicente Vargas</v>
+        <v>Vicente Pérez</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="43">
@@ -1297,19 +1424,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Sofía López</v>
+        <v>Sofía Pérez</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E43" s="2">
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="44">
@@ -1317,19 +1447,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Santiago Romero</v>
+        <v>Mateo González</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="45">
@@ -1337,19 +1470,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Valentina González</v>
+        <v>Valentina Pérez</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D45" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E45" s="2">
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="46">
@@ -1357,18 +1493,21 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Sebastián Herrera</v>
+        <v>Santiago Díaz</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1377,19 +1516,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Isabella Martínez</v>
+        <v>Camila Silva</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="48">
@@ -1397,19 +1539,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Matías Díaz</v>
+        <v>Sebastián Pérez</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>5</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="49">
@@ -1417,18 +1562,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Camila Vargas</v>
+        <v>Mariana Díaz</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>4.8</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1437,19 +1585,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Benjamín Flores</v>
+        <v>Matías Castro</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="3">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>5.7</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="51">
@@ -1457,18 +1608,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Mariana Rojas</v>
+        <v>Lucía Flores</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>4.4</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1477,19 +1631,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Tomás Jiménez</v>
+        <v>Benjamín Martínez</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="3">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>6.1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="53">
@@ -1497,19 +1654,22 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Lucía Díaz</v>
+        <v>Martina Silva</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="54">
@@ -1517,19 +1677,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Diego Castro</v>
+        <v>Nicolás Jiménez</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="55">
@@ -1537,19 +1700,22 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Martina Gutiérrez</v>
+        <v>Daniela Herrera</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>4</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="56">
@@ -1557,18 +1723,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Emiliano González</v>
+        <v>Joaquín Flores</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>4.7</v>
+      </c>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1577,19 +1746,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Daniela Díaz</v>
+        <v>Gabriela Castro</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="58">
@@ -1597,19 +1769,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Gabriel Ramírez</v>
+        <v>Diego Rodríguez</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="59">
@@ -1617,19 +1792,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Gabriela Silva</v>
+        <v>Victoria Romero</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="60">
@@ -1637,19 +1815,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Lucas Martínez</v>
+        <v>Emiliano Rojas</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D60" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="61">
@@ -1657,19 +1838,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Victoria Jiménez</v>
+        <v>Renata Romero</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>B</v>
+        <v>✓</v>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="62">
@@ -1677,19 +1861,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Martín Jiménez</v>
+        <v>Gabriel Díaz</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>D</v>
+        <v>✓</v>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="63">
@@ -1697,18 +1884,21 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Renata Muñoz</v>
+        <v>Emilia González</v>
       </c>
       <c r="C63" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D63" s="3">
-        <v>6</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E63" s="2">
+        <v>3</v>
       </c>
       <c r="F63" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G63" s="2" t="str">
         <v>A</v>
       </c>
     </row>
@@ -1717,19 +1907,22 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Felipe Rodríguez</v>
+        <v>Lucas Jiménez</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>A</v>
+        <v>✓</v>
+      </c>
+      <c r="G64" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="65">
@@ -1737,7 +1930,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Florencia Ramírez</v>
+        <v>Florencia Herrera</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
@@ -1745,10 +1938,13 @@
       <c r="D65" s="3">
         <v>5.1</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1757,18 +1953,21 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Alejandro López</v>
+        <v>Martín Morales</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E66" s="2">
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -1777,18 +1976,21 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Paula Rodríguez</v>
+        <v>Paula Pérez</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>D</v>
       </c>
     </row>
@@ -1797,18 +1999,21 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Samuel Silva</v>
+        <v>Felipe Silva</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1817,19 +2022,22 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Antonella Herrera</v>
+        <v>Antonella Díaz</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="70">
@@ -1837,19 +2045,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Agustín Castro</v>
+        <v>Alejandro Silva</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="3">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="71">
@@ -1857,19 +2068,22 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Josefa Vargas</v>
+        <v>Josefa Morales</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E71" s="2">
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="72">
@@ -1877,19 +2091,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Daniel Herrera</v>
+        <v>Agustín Vargas</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>D</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -1897,19 +2114,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Catalina Rodríguez</v>
+        <v>Catalina Jiménez</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v>✓</v>
+        <v>5.4</v>
+      </c>
+      <c r="E73" s="2">
+        <v>4</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="74">
@@ -1917,19 +2137,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Maximiliano Jiménez</v>
+        <v>Daniel Silva</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="3">
-        <v>5.4</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v>✓</v>
+        <v>5.7</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="75">
@@ -1937,19 +2160,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Ximena Flores</v>
+        <v>Ximena Martínez</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>A</v>
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="76">
@@ -1957,19 +2183,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Vicente Gutiérrez</v>
+        <v>Maximiliano Morales</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="3">
-        <v>6.4</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E76" s="2">
+        <v>5</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="77">
@@ -1977,18 +2206,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Julieta Morales</v>
+        <v>Julieta Rojas</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>5.2</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
       </c>
       <c r="F77" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
         <v>B</v>
       </c>
     </row>
@@ -1997,19 +2229,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Mateo Vargas</v>
+        <v>Vicente Silva</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="79">
@@ -2017,19 +2252,22 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Agustina Romero</v>
+        <v>Agustina Ramírez</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>4.9</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>B</v>
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
+        <v>D</v>
       </c>
     </row>
     <row r="80">
@@ -2037,19 +2275,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Sebastián Romero</v>
+        <v>Mateo Morales</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>5.9</v>
+      </c>
+      <c r="E80" s="2">
+        <v>4</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>C</v>
+        <v>✓</v>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
     <row r="81">
@@ -2057,18 +2298,21 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Sofía Herrera</v>
+        <v>Sofía Rojas</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>5.1</v>
+      </c>
+      <c r="E81" s="2">
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
         <v>C</v>
       </c>
     </row>
@@ -2077,24 +2321,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Matías Morales</v>
+        <v>Santiago Pérez</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="3">
-        <v>5.1</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>4.3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>C</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2105,13 +2352,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2127,21 +2374,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2149,4 +2396,87 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Criterio</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opciones</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Género</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Promedio de notas</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nivel de matemática</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nivel</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Grupo de origen</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>